--- a/儲槽作業日報/TK604_2026_Temperature_Report.xlsx
+++ b/儲槽作業日報/TK604_2026_Temperature_Report.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GOOGLE ANGET\儲槽作業日報\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="2026_Temperature" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -616,13 +621,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -650,16 +662,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -678,11 +708,14 @@
         </c:rich>
       </c:tx>
       <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1508,7 +1541,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>13</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>23</c:v>
@@ -1610,7 +1643,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>14</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>24</c:v>
@@ -1927,6 +1960,12 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B632-44E5-A401-093A10BA1DB2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -3172,8 +3211,22 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B632-44E5-A401-093A10BA1DB2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:marker val="1"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:lineChart>
@@ -3182,22 +3235,30 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -3207,8 +3268,11 @@
     <c:legend>
       <c:legendPos val="r"/>
       <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -3219,8 +3283,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3239,11 +3313,14 @@
         </c:rich>
       </c:tx>
       <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -4171,7 +4248,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>14</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>24</c:v>
@@ -4488,6 +4565,12 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4945-4AA4-8902-F3AE42E123EB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -5733,8 +5816,22 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4945-4AA4-8902-F3AE42E123EB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:marker val="1"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:lineChart>
@@ -5743,22 +5840,30 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -5768,8 +5873,11 @@
     <c:legend>
       <c:legendPos val="r"/>
       <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -5789,8 +5897,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -5845,7 +5953,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -5887,7 +5995,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5919,9 +6027,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5953,6 +6062,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -6128,11 +6238,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E204"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6149,7 +6259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6166,7 +6276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6183,7 +6293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6200,7 +6310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6217,7 +6327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6234,7 +6344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -6251,7 +6361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6268,7 +6378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6285,7 +6395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -6302,7 +6412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6319,7 +6429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6336,7 +6446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6353,7 +6463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6370,7 +6480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6387,7 +6497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -6404,7 +6514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -6421,7 +6531,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -6438,7 +6548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -6455,7 +6565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -6472,7 +6582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -6489,7 +6599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -6506,7 +6616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -6523,7 +6633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -6540,7 +6650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -6557,7 +6667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -6574,7 +6684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -6591,7 +6701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -6608,7 +6718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -6625,7 +6735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -6642,7 +6752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -6659,7 +6769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -6676,7 +6786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -6693,7 +6803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -6710,7 +6820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -6727,7 +6837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -6744,7 +6854,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -6761,7 +6871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -6778,7 +6888,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -6795,7 +6905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -6812,7 +6922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -6829,7 +6939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -6846,7 +6956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -6863,7 +6973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -6880,7 +6990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -6897,7 +7007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -6914,7 +7024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -6931,7 +7041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -6948,7 +7058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -6965,7 +7075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -6982,7 +7092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -6999,7 +7109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -7016,7 +7126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -7033,7 +7143,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -7050,7 +7160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -7067,7 +7177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -7084,7 +7194,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -7101,7 +7211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -7118,7 +7228,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -7135,7 +7245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -7152,7 +7262,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -7169,7 +7279,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -7186,7 +7296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -7203,7 +7313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -7220,7 +7330,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -7237,12 +7347,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C66">
         <v>18</v>
@@ -7254,7 +7364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -7271,7 +7381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -7288,7 +7398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -7305,7 +7415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -7322,7 +7432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -7339,7 +7449,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -7356,7 +7466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -7373,7 +7483,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -7390,7 +7500,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -7407,7 +7517,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -7424,7 +7534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -7441,7 +7551,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -7458,7 +7568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -7475,7 +7585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -7492,7 +7602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -7509,7 +7619,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -7526,7 +7636,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -7543,7 +7653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -7560,7 +7670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -7577,7 +7687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -7594,7 +7704,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -7611,7 +7721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -7628,7 +7738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -7645,7 +7755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -7662,7 +7772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -7679,7 +7789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -7696,7 +7806,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -7713,7 +7823,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -7730,7 +7840,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -7747,7 +7857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -7764,7 +7874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -7781,7 +7891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -7798,7 +7908,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -7815,15 +7925,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D100">
         <v>28</v>
@@ -7832,7 +7942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -7849,7 +7959,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -7866,7 +7976,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -7883,7 +7993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -7900,7 +8010,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -7917,7 +8027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -7934,7 +8044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -7951,7 +8061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -7968,7 +8078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -7985,7 +8095,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -8002,7 +8112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -8019,7 +8129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -8036,7 +8146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -8053,7 +8163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -8070,7 +8180,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -8087,7 +8197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -8104,7 +8214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -8121,7 +8231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -8138,7 +8248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -8155,7 +8265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -8172,7 +8282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>119</v>
       </c>
@@ -8189,7 +8299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -8206,7 +8316,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -8223,7 +8333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -8240,7 +8350,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -8257,7 +8367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>124</v>
       </c>
@@ -8274,7 +8384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -8291,7 +8401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -8308,7 +8418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -8325,7 +8435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -8342,7 +8452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -8359,7 +8469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -8376,7 +8486,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -8393,7 +8503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -8410,7 +8520,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -8427,7 +8537,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>133</v>
       </c>
@@ -8444,7 +8554,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>134</v>
       </c>
@@ -8461,7 +8571,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>135</v>
       </c>
@@ -8478,7 +8588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>136</v>
       </c>
@@ -8495,7 +8605,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>137</v>
       </c>
@@ -8512,7 +8622,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>138</v>
       </c>
@@ -8529,7 +8639,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -8546,7 +8656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -8563,7 +8673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>141</v>
       </c>
@@ -8580,7 +8690,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>142</v>
       </c>
@@ -8597,7 +8707,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -8614,7 +8724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>144</v>
       </c>
@@ -8631,7 +8741,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>145</v>
       </c>
@@ -8648,7 +8758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>146</v>
       </c>
@@ -8665,7 +8775,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>147</v>
       </c>
@@ -8682,7 +8792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>148</v>
       </c>
@@ -8699,7 +8809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>149</v>
       </c>
@@ -8716,7 +8826,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>149</v>
       </c>
@@ -8733,7 +8843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>150</v>
       </c>
@@ -8750,7 +8860,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>151</v>
       </c>
@@ -8767,7 +8877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>152</v>
       </c>
@@ -8784,7 +8894,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -8801,7 +8911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>154</v>
       </c>
@@ -8818,7 +8928,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>155</v>
       </c>
@@ -8835,7 +8945,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>156</v>
       </c>
@@ -8852,7 +8962,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>157</v>
       </c>
@@ -8869,7 +8979,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>158</v>
       </c>
@@ -8886,7 +8996,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>159</v>
       </c>
@@ -8903,7 +9013,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>160</v>
       </c>
@@ -8920,7 +9030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>161</v>
       </c>
@@ -8937,7 +9047,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>162</v>
       </c>
@@ -8954,7 +9064,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>163</v>
       </c>
@@ -8971,7 +9081,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>164</v>
       </c>
@@ -8988,7 +9098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>165</v>
       </c>
@@ -9005,7 +9115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>166</v>
       </c>
@@ -9022,7 +9132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>167</v>
       </c>
@@ -9039,7 +9149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>168</v>
       </c>
@@ -9056,7 +9166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>169</v>
       </c>
@@ -9073,7 +9183,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>170</v>
       </c>
@@ -9090,7 +9200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>171</v>
       </c>
@@ -9107,7 +9217,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>171</v>
       </c>
@@ -9124,7 +9234,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>172</v>
       </c>
@@ -9141,7 +9251,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>173</v>
       </c>
@@ -9158,7 +9268,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>174</v>
       </c>
@@ -9175,7 +9285,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>175</v>
       </c>
@@ -9192,7 +9302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>176</v>
       </c>
@@ -9209,7 +9319,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>177</v>
       </c>
@@ -9226,7 +9336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>178</v>
       </c>
@@ -9243,7 +9353,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>179</v>
       </c>
@@ -9260,7 +9370,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>180</v>
       </c>
@@ -9277,7 +9387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>181</v>
       </c>
@@ -9294,7 +9404,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>182</v>
       </c>
@@ -9311,7 +9421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>183</v>
       </c>
@@ -9328,7 +9438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>184</v>
       </c>
@@ -9345,7 +9455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>185</v>
       </c>
@@ -9362,7 +9472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>186</v>
       </c>
@@ -9379,7 +9489,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>187</v>
       </c>
@@ -9396,7 +9506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>188</v>
       </c>
@@ -9413,7 +9523,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>189</v>
       </c>
@@ -9430,7 +9540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>190</v>
       </c>
@@ -9447,7 +9557,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>191</v>
       </c>
@@ -9464,7 +9574,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>191</v>
       </c>
@@ -9481,7 +9591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>192</v>
       </c>
@@ -9498,7 +9608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>193</v>
       </c>
@@ -9515,7 +9625,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>194</v>
       </c>
@@ -9532,7 +9642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>195</v>
       </c>
@@ -9549,7 +9659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>196</v>
       </c>
@@ -9566,7 +9676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>197</v>
       </c>
@@ -9583,7 +9693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>198</v>
       </c>
@@ -9601,6 +9711,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
